--- a/dl/191ea4ec9c222f223382/Numbersmith_Mortgage_and_Loan_Payoff_Calculator.xlsx
+++ b/dl/191ea4ec9c222f223382/Numbersmith_Mortgage_and_Loan_Payoff_Calculator.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t xml:space="preserve">Numbersmith - Mortgage and Loan Payoff Calculator</t>
   </si>
@@ -87,6 +87,9 @@
     <t xml:space="preserve">Months saved</t>
   </si>
   <si>
+    <t xml:space="preserve">Extra monthly starts at payment # (1=now)</t>
+  </si>
+  <si>
     <t xml:space="preserve">New payoff date</t>
   </si>
   <si>
@@ -129,7 +132,7 @@
     <t xml:space="preserve">Schedule - Full Amortization With Extra Payments</t>
   </si>
   <si>
-    <t xml:space="preserve">Formula-driven month-by-month schedule using the Calculator inputs. Extra payments are capped with MIN so the loan never overshoots a zero balance.</t>
+    <t xml:space="preserve">Formula-driven month-by-month schedule using the Calculator inputs. Extra payments are capped with MIN so the loan never overshoots a zero balance. The monthly extra begins at the start payment number on the Calculator tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Rows run up to 480 months (40 years). Once the balance reaches zero, every later row shows zero.</t>
@@ -6696,11 +6699,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="73070129"/>
-        <c:axId val="26769321"/>
+        <c:axId val="13238680"/>
+        <c:axId val="74771503"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="73070129"/>
+        <c:axId val="13238680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6766,7 +6769,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26769321"/>
+        <c:crossAx val="74771503"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6774,7 +6777,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26769321"/>
+        <c:axId val="74771503"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6850,7 +6853,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73070129"/>
+        <c:crossAx val="13238680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7591,11 +7594,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="33834504"/>
-        <c:axId val="66910923"/>
+        <c:axId val="21424876"/>
+        <c:axId val="64649282"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="33834504"/>
+        <c:axId val="21424876"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7661,7 +7664,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66910923"/>
+        <c:crossAx val="64649282"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7669,7 +7672,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66910923"/>
+        <c:axId val="64649282"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7745,7 +7748,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33834504"/>
+        <c:crossAx val="21424876"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8243,9 +8246,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>181080</xdr:colOff>
+      <xdr:colOff>180720</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>159840</xdr:rowOff>
+      <xdr:rowOff>159480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -8254,7 +8257,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="1085760"/>
-        <a:ext cx="8639280" cy="3779280"/>
+        <a:ext cx="8638920" cy="3778920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8273,9 +8276,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>181080</xdr:colOff>
+      <xdr:colOff>180720</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>159840</xdr:rowOff>
+      <xdr:rowOff>159480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -8284,7 +8287,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3383280" y="5467320"/>
-        <a:ext cx="8639280" cy="3779280"/>
+        <a:ext cx="8638920" cy="3778920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8640,8 +8643,14 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="G11" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="16" t="n">
         <f aca="false">INDEX(Schedule!B6:B485,COUNTIF(Schedule!D6:D485,"&gt;0"))</f>
@@ -8650,7 +8659,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -8660,21 +8669,21 @@
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
       <c r="B14" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="18" t="n">
         <f aca="false">INDEX(Baseline!B6:B485,COUNTIF(Baseline!D6:D485,"&gt;0"))</f>
@@ -8695,7 +8704,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="16" t="n">
         <f aca="false">H11</f>
@@ -8716,7 +8725,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -8728,17 +8737,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -8750,7 +8759,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -8805,7 +8814,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8820,7 +8829,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8835,7 +8844,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -8850,42 +8859,42 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J5" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">Calculator!$B$9</f>
@@ -8908,7 +8917,7 @@
         <v>379.69</v>
       </c>
       <c r="G6" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A6=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B6)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A6&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A6=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B6)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H6" s="26" t="n">
@@ -8954,7 +8963,7 @@
         <v>382.83</v>
       </c>
       <c r="G7" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A7=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B7)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A7&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A7=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B7)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H7" s="26" t="n">
@@ -9000,7 +9009,7 @@
         <v>385.99</v>
       </c>
       <c r="G8" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A8=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B8)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A8&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A8=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B8)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H8" s="26" t="n">
@@ -9046,7 +9055,7 @@
         <v>394.58</v>
       </c>
       <c r="G9" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A9=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B9)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A9&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A9=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B9)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H9" s="26" t="n">
@@ -9092,7 +9101,7 @@
         <v>397.8</v>
       </c>
       <c r="G10" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A10=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B10)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A10&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A10=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B10)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H10" s="26" t="n">
@@ -9138,7 +9147,7 @@
         <v>401.04</v>
       </c>
       <c r="G11" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A11=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B11)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A11&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A11=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B11)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H11" s="26" t="n">
@@ -9184,7 +9193,7 @@
         <v>404.29</v>
       </c>
       <c r="G12" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A12=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B12)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A12&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A12=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B12)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H12" s="26" t="n">
@@ -9230,7 +9239,7 @@
         <v>407.57</v>
       </c>
       <c r="G13" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A13=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B13)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A13&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A13=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B13)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H13" s="26" t="n">
@@ -9276,7 +9285,7 @@
         <v>410.86</v>
       </c>
       <c r="G14" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A14=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B14)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A14&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A14=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B14)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H14" s="26" t="n">
@@ -9322,7 +9331,7 @@
         <v>414.17</v>
       </c>
       <c r="G15" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A15=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B15)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A15&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A15=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B15)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H15" s="26" t="n">
@@ -9368,7 +9377,7 @@
         <v>417.49</v>
       </c>
       <c r="G16" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A16=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B16)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A16&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A16=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B16)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H16" s="26" t="n">
@@ -9414,7 +9423,7 @@
         <v>420.84</v>
       </c>
       <c r="G17" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A17=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B17)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A17&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A17=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B17)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>3200</v>
       </c>
       <c r="H17" s="26" t="n">
@@ -9460,7 +9469,7 @@
         <v>440.45</v>
       </c>
       <c r="G18" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A18=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B18)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A18&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A18=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B18)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H18" s="26" t="n">
@@ -9506,7 +9515,7 @@
         <v>443.92</v>
       </c>
       <c r="G19" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A19=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B19)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A19&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A19=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B19)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H19" s="26" t="n">
@@ -9552,7 +9561,7 @@
         <v>447.41</v>
       </c>
       <c r="G20" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A20=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B20)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A20&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A20=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B20)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H20" s="26" t="n">
@@ -9598,7 +9607,7 @@
         <v>456.33</v>
       </c>
       <c r="G21" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A21=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B21)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A21&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A21=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B21)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H21" s="26" t="n">
@@ -9644,7 +9653,7 @@
         <v>459.89</v>
       </c>
       <c r="G22" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A22=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B22)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A22&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A22=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B22)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H22" s="26" t="n">
@@ -9690,7 +9699,7 @@
         <v>463.46</v>
       </c>
       <c r="G23" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A23=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B23)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A23&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A23=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B23)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H23" s="26" t="n">
@@ -9736,7 +9745,7 @@
         <v>467.05</v>
       </c>
       <c r="G24" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A24=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B24)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A24&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A24=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B24)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H24" s="26" t="n">
@@ -9782,7 +9791,7 @@
         <v>470.67</v>
       </c>
       <c r="G25" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A25=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B25)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A25&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A25=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B25)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H25" s="26" t="n">
@@ -9828,7 +9837,7 @@
         <v>474.3</v>
       </c>
       <c r="G26" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A26=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B26)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A26&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A26=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B26)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H26" s="26" t="n">
@@ -9874,7 +9883,7 @@
         <v>477.95</v>
       </c>
       <c r="G27" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A27=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B27)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A27&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A27=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B27)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H27" s="26" t="n">
@@ -9920,7 +9929,7 @@
         <v>481.62</v>
       </c>
       <c r="G28" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A28=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B28)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A28&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A28=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B28)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H28" s="26" t="n">
@@ -9966,7 +9975,7 @@
         <v>485.32</v>
       </c>
       <c r="G29" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A29=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B29)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A29&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A29=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B29)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H29" s="26" t="n">
@@ -10012,7 +10021,7 @@
         <v>489.03</v>
       </c>
       <c r="G30" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A30=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B30)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A30&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A30=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B30)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H30" s="26" t="n">
@@ -10058,7 +10067,7 @@
         <v>492.76</v>
       </c>
       <c r="G31" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A31=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B31)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A31&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A31=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B31)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H31" s="26" t="n">
@@ -10104,7 +10113,7 @@
         <v>496.51</v>
       </c>
       <c r="G32" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A32=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B32)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A32&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A32=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B32)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H32" s="26" t="n">
@@ -10150,7 +10159,7 @@
         <v>505.7</v>
       </c>
       <c r="G33" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A33=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B33)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A33&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A33=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B33)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H33" s="26" t="n">
@@ -10196,7 +10205,7 @@
         <v>509.52</v>
       </c>
       <c r="G34" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A34=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B34)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A34&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A34=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B34)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H34" s="26" t="n">
@@ -10242,7 +10251,7 @@
         <v>513.37</v>
       </c>
       <c r="G35" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A35=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B35)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A35&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A35=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B35)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H35" s="26" t="n">
@@ -10288,7 +10297,7 @@
         <v>517.23</v>
       </c>
       <c r="G36" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A36=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B36)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A36&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A36=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B36)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H36" s="26" t="n">
@@ -10334,7 +10343,7 @@
         <v>521.12</v>
       </c>
       <c r="G37" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A37=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B37)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A37&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A37=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B37)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H37" s="26" t="n">
@@ -10380,7 +10389,7 @@
         <v>525.02</v>
       </c>
       <c r="G38" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A38=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B38)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A38&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A38=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B38)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H38" s="26" t="n">
@@ -10426,7 +10435,7 @@
         <v>528.95</v>
       </c>
       <c r="G39" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A39=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B39)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A39&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A39=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B39)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H39" s="26" t="n">
@@ -10472,7 +10481,7 @@
         <v>532.9</v>
       </c>
       <c r="G40" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A40=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B40)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A40&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A40=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B40)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H40" s="26" t="n">
@@ -10518,7 +10527,7 @@
         <v>536.87</v>
       </c>
       <c r="G41" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A41=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B41)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A41&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A41=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B41)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H41" s="26" t="n">
@@ -10564,7 +10573,7 @@
         <v>540.86</v>
       </c>
       <c r="G42" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A42=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B42)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A42&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A42=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B42)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H42" s="26" t="n">
@@ -10610,7 +10619,7 @@
         <v>544.87</v>
       </c>
       <c r="G43" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A43=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B43)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A43&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A43=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B43)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H43" s="26" t="n">
@@ -10656,7 +10665,7 @@
         <v>548.91</v>
       </c>
       <c r="G44" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A44=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B44)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A44&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A44=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B44)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H44" s="26" t="n">
@@ -10702,7 +10711,7 @@
         <v>558.38</v>
       </c>
       <c r="G45" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A45=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B45)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A45&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A45=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B45)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H45" s="26" t="n">
@@ -10748,7 +10757,7 @@
         <v>562.49</v>
       </c>
       <c r="G46" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A46=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B46)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A46&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A46=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B46)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H46" s="26" t="n">
@@ -10794,7 +10803,7 @@
         <v>566.62</v>
       </c>
       <c r="G47" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A47=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B47)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A47&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A47=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B47)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H47" s="26" t="n">
@@ -10840,7 +10849,7 @@
         <v>570.77</v>
       </c>
       <c r="G48" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A48=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B48)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A48&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A48=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B48)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H48" s="26" t="n">
@@ -10886,7 +10895,7 @@
         <v>574.95</v>
       </c>
       <c r="G49" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A49=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B49)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A49&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A49=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B49)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H49" s="26" t="n">
@@ -10932,7 +10941,7 @@
         <v>579.14</v>
       </c>
       <c r="G50" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A50=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B50)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A50&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A50=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B50)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H50" s="26" t="n">
@@ -10978,7 +10987,7 @@
         <v>583.36</v>
       </c>
       <c r="G51" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A51=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B51)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A51&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A51=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B51)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H51" s="26" t="n">
@@ -11024,7 +11033,7 @@
         <v>587.61</v>
       </c>
       <c r="G52" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A52=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B52)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A52&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A52=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B52)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H52" s="26" t="n">
@@ -11070,7 +11079,7 @@
         <v>591.87</v>
       </c>
       <c r="G53" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A53=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B53)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A53&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A53=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B53)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H53" s="26" t="n">
@@ -11116,7 +11125,7 @@
         <v>596.16</v>
       </c>
       <c r="G54" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A54=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B54)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A54&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A54=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B54)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H54" s="26" t="n">
@@ -11162,7 +11171,7 @@
         <v>600.48</v>
       </c>
       <c r="G55" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A55=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B55)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A55&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A55=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B55)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H55" s="26" t="n">
@@ -11208,7 +11217,7 @@
         <v>604.81</v>
       </c>
       <c r="G56" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A56=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B56)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A56&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A56=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B56)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H56" s="26" t="n">
@@ -11254,7 +11263,7 @@
         <v>614.59</v>
       </c>
       <c r="G57" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A57=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B57)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A57&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A57=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B57)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H57" s="26" t="n">
@@ -11300,7 +11309,7 @@
         <v>619</v>
       </c>
       <c r="G58" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A58=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B58)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A58&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A58=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B58)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H58" s="26" t="n">
@@ -11346,7 +11355,7 @@
         <v>623.44</v>
       </c>
       <c r="G59" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A59=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B59)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A59&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A59=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B59)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H59" s="26" t="n">
@@ -11392,7 +11401,7 @@
         <v>627.9</v>
       </c>
       <c r="G60" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A60=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B60)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A60&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A60=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B60)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H60" s="26" t="n">
@@ -11438,7 +11447,7 @@
         <v>632.38</v>
       </c>
       <c r="G61" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A61=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B61)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A61&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A61=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B61)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H61" s="26" t="n">
@@ -11484,7 +11493,7 @@
         <v>636.89</v>
       </c>
       <c r="G62" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A62=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B62)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A62&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A62=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B62)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H62" s="26" t="n">
@@ -11530,7 +11539,7 @@
         <v>641.42</v>
       </c>
       <c r="G63" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A63=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B63)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A63&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A63=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B63)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H63" s="26" t="n">
@@ -11576,7 +11585,7 @@
         <v>645.98</v>
       </c>
       <c r="G64" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A64=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B64)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A64&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A64=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B64)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H64" s="26" t="n">
@@ -11622,7 +11631,7 @@
         <v>650.56</v>
       </c>
       <c r="G65" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A65=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B65)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A65&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A65=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B65)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H65" s="26" t="n">
@@ -11668,7 +11677,7 @@
         <v>655.17</v>
       </c>
       <c r="G66" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A66=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B66)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A66&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A66=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B66)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H66" s="26" t="n">
@@ -11714,7 +11723,7 @@
         <v>659.8</v>
       </c>
       <c r="G67" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A67=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B67)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A67&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A67=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B67)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H67" s="26" t="n">
@@ -11760,7 +11769,7 @@
         <v>664.46</v>
       </c>
       <c r="G68" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A68=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B68)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A68&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A68=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B68)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H68" s="26" t="n">
@@ -11806,7 +11815,7 @@
         <v>674.56</v>
       </c>
       <c r="G69" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A69=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B69)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A69&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A69=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B69)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H69" s="26" t="n">
@@ -11852,7 +11861,7 @@
         <v>679.3</v>
       </c>
       <c r="G70" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A70=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B70)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A70&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A70=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B70)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H70" s="26" t="n">
@@ -11898,7 +11907,7 @@
         <v>684.06</v>
       </c>
       <c r="G71" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A71=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B71)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A71&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A71=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B71)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H71" s="26" t="n">
@@ -11944,7 +11953,7 @@
         <v>688.85</v>
       </c>
       <c r="G72" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A72=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B72)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A72&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A72=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B72)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H72" s="26" t="n">
@@ -11990,7 +11999,7 @@
         <v>693.66</v>
       </c>
       <c r="G73" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A73=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B73)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A73&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A73=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B73)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H73" s="26" t="n">
@@ -12036,7 +12045,7 @@
         <v>698.5</v>
       </c>
       <c r="G74" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A74=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B74)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A74&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A74=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B74)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H74" s="26" t="n">
@@ -12082,7 +12091,7 @@
         <v>703.37</v>
       </c>
       <c r="G75" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A75=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B75)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A75&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A75=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B75)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H75" s="26" t="n">
@@ -12128,7 +12137,7 @@
         <v>708.26</v>
       </c>
       <c r="G76" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A76=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B76)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A76&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A76=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B76)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H76" s="26" t="n">
@@ -12174,7 +12183,7 @@
         <v>713.18</v>
       </c>
       <c r="G77" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A77=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B77)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A77&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A77=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B77)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H77" s="26" t="n">
@@ -12220,7 +12229,7 @@
         <v>718.13</v>
       </c>
       <c r="G78" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A78=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B78)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A78&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A78=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B78)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H78" s="26" t="n">
@@ -12266,7 +12275,7 @@
         <v>723.1</v>
       </c>
       <c r="G79" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A79=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B79)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A79&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A79=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B79)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H79" s="26" t="n">
@@ -12312,7 +12321,7 @@
         <v>728.1</v>
       </c>
       <c r="G80" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A80=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B80)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A80&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A80=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B80)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H80" s="26" t="n">
@@ -12358,7 +12367,7 @@
         <v>738.55</v>
       </c>
       <c r="G81" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A81=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B81)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A81&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A81=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B81)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H81" s="26" t="n">
@@ -12404,7 +12413,7 @@
         <v>743.63</v>
       </c>
       <c r="G82" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A82=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B82)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A82&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A82=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B82)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H82" s="26" t="n">
@@ -12450,7 +12459,7 @@
         <v>748.74</v>
       </c>
       <c r="G83" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A83=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B83)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A83&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A83=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B83)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H83" s="26" t="n">
@@ -12496,7 +12505,7 @@
         <v>753.88</v>
       </c>
       <c r="G84" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A84=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B84)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A84&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A84=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B84)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H84" s="26" t="n">
@@ -12542,7 +12551,7 @@
         <v>759.05</v>
       </c>
       <c r="G85" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A85=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B85)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A85&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A85=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B85)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H85" s="26" t="n">
@@ -12588,7 +12597,7 @@
         <v>764.24</v>
       </c>
       <c r="G86" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A86=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B86)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A86&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A86=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B86)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H86" s="26" t="n">
@@ -12634,7 +12643,7 @@
         <v>769.47</v>
       </c>
       <c r="G87" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A87=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B87)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A87&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A87=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B87)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H87" s="26" t="n">
@@ -12680,7 +12689,7 @@
         <v>774.72</v>
       </c>
       <c r="G88" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A88=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B88)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A88&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A88=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B88)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H88" s="26" t="n">
@@ -12726,7 +12735,7 @@
         <v>780</v>
       </c>
       <c r="G89" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A89=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B89)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A89&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A89=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B89)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H89" s="26" t="n">
@@ -12772,7 +12781,7 @@
         <v>785.3</v>
       </c>
       <c r="G90" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A90=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B90)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A90&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A90=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B90)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H90" s="26" t="n">
@@ -12818,7 +12827,7 @@
         <v>790.64</v>
       </c>
       <c r="G91" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A91=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B91)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A91&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A91=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B91)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H91" s="26" t="n">
@@ -12864,7 +12873,7 @@
         <v>796.01</v>
       </c>
       <c r="G92" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A92=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B92)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A92&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A92=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B92)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H92" s="26" t="n">
@@ -12910,7 +12919,7 @@
         <v>806.82</v>
       </c>
       <c r="G93" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A93=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B93)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A93&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A93=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B93)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H93" s="26" t="n">
@@ -12956,7 +12965,7 @@
         <v>812.27</v>
       </c>
       <c r="G94" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A94=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B94)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A94&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A94=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B94)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H94" s="26" t="n">
@@ -13002,7 +13011,7 @@
         <v>817.76</v>
       </c>
       <c r="G95" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A95=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B95)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A95&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A95=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B95)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H95" s="26" t="n">
@@ -13048,7 +13057,7 @@
         <v>823.27</v>
       </c>
       <c r="G96" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A96=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B96)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A96&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A96=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B96)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H96" s="26" t="n">
@@ -13094,7 +13103,7 @@
         <v>828.81</v>
       </c>
       <c r="G97" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A97=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B97)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A97&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A97=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B97)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H97" s="26" t="n">
@@ -13140,7 +13149,7 @@
         <v>834.38</v>
       </c>
       <c r="G98" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A98=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B98)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A98&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A98=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B98)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H98" s="26" t="n">
@@ -13186,7 +13195,7 @@
         <v>839.99</v>
       </c>
       <c r="G99" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A99=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B99)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A99&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A99=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B99)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H99" s="26" t="n">
@@ -13232,7 +13241,7 @@
         <v>845.62</v>
       </c>
       <c r="G100" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A100=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B100)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A100&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A100=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B100)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H100" s="26" t="n">
@@ -13278,7 +13287,7 @@
         <v>851.28</v>
       </c>
       <c r="G101" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A101=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B101)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A101&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A101=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B101)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H101" s="26" t="n">
@@ -13324,7 +13333,7 @@
         <v>856.98</v>
       </c>
       <c r="G102" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A102=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B102)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A102&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A102=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B102)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H102" s="26" t="n">
@@ -13370,7 +13379,7 @@
         <v>862.7</v>
       </c>
       <c r="G103" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A103=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B103)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A103&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A103=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B103)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H103" s="26" t="n">
@@ -13416,7 +13425,7 @@
         <v>868.46</v>
       </c>
       <c r="G104" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A104=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B104)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A104&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A104=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B104)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H104" s="26" t="n">
@@ -13462,7 +13471,7 @@
         <v>879.66</v>
       </c>
       <c r="G105" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A105=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B105)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A105&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A105=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B105)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H105" s="26" t="n">
@@ -13508,7 +13517,7 @@
         <v>885.51</v>
       </c>
       <c r="G106" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A106=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B106)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A106&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A106=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B106)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H106" s="26" t="n">
@@ -13554,7 +13563,7 @@
         <v>891.39</v>
       </c>
       <c r="G107" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A107=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B107)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A107&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A107=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B107)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H107" s="26" t="n">
@@ -13600,7 +13609,7 @@
         <v>897.3</v>
       </c>
       <c r="G108" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A108=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B108)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A108&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A108=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B108)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H108" s="26" t="n">
@@ -13646,7 +13655,7 @@
         <v>903.25</v>
       </c>
       <c r="G109" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A109=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B109)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A109&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A109=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B109)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H109" s="26" t="n">
@@ -13692,7 +13701,7 @@
         <v>909.22</v>
       </c>
       <c r="G110" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A110=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B110)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A110&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A110=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B110)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H110" s="26" t="n">
@@ -13738,7 +13747,7 @@
         <v>915.23</v>
       </c>
       <c r="G111" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A111=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B111)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A111&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A111=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B111)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H111" s="26" t="n">
@@ -13784,7 +13793,7 @@
         <v>921.27</v>
       </c>
       <c r="G112" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A112=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B112)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A112&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A112=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B112)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H112" s="26" t="n">
@@ -13830,7 +13839,7 @@
         <v>927.35</v>
       </c>
       <c r="G113" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A113=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B113)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A113&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A113=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B113)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H113" s="26" t="n">
@@ -13876,7 +13885,7 @@
         <v>933.45</v>
       </c>
       <c r="G114" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A114=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B114)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A114&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A114=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B114)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H114" s="26" t="n">
@@ -13922,7 +13931,7 @@
         <v>939.59</v>
       </c>
       <c r="G115" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A115=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B115)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A115&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A115=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B115)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H115" s="26" t="n">
@@ -13968,7 +13977,7 @@
         <v>945.77</v>
       </c>
       <c r="G116" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A116=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B116)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A116&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A116=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B116)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H116" s="26" t="n">
@@ -14014,7 +14023,7 @@
         <v>957.39</v>
       </c>
       <c r="G117" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A117=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B117)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A117&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A117=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B117)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H117" s="26" t="n">
@@ -14060,7 +14069,7 @@
         <v>963.66</v>
       </c>
       <c r="G118" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A118=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B118)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A118&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A118=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B118)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H118" s="26" t="n">
@@ -14106,7 +14115,7 @@
         <v>969.96</v>
       </c>
       <c r="G119" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A119=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B119)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A119&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A119=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B119)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H119" s="26" t="n">
@@ -14152,7 +14161,7 @@
         <v>976.3</v>
       </c>
       <c r="G120" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A120=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B120)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A120&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A120=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B120)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H120" s="26" t="n">
@@ -14198,7 +14207,7 @@
         <v>982.67</v>
       </c>
       <c r="G121" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A121=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B121)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A121&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A121=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B121)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H121" s="26" t="n">
@@ -14244,7 +14253,7 @@
         <v>989.08</v>
       </c>
       <c r="G122" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A122=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B122)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A122&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A122=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B122)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H122" s="26" t="n">
@@ -14290,7 +14299,7 @@
         <v>995.52</v>
       </c>
       <c r="G123" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A123=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B123)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A123&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A123=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B123)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H123" s="26" t="n">
@@ -14336,7 +14345,7 @@
         <v>1001.99</v>
       </c>
       <c r="G124" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A124=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B124)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A124&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A124=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B124)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H124" s="26" t="n">
@@ -14382,7 +14391,7 @@
         <v>1008.5</v>
       </c>
       <c r="G125" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A125=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B125)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A125&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A125=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B125)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H125" s="26" t="n">
@@ -14428,7 +14437,7 @@
         <v>1015.05</v>
       </c>
       <c r="G126" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A126=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B126)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A126&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A126=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B126)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H126" s="26" t="n">
@@ -14474,7 +14483,7 @@
         <v>1021.63</v>
       </c>
       <c r="G127" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A127=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B127)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A127&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A127=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B127)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H127" s="26" t="n">
@@ -14520,7 +14529,7 @@
         <v>1028.25</v>
       </c>
       <c r="G128" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A128=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B128)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A128&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A128=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B128)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H128" s="26" t="n">
@@ -14566,7 +14575,7 @@
         <v>1040.32</v>
       </c>
       <c r="G129" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A129=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B129)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A129&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A129=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B129)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H129" s="26" t="n">
@@ -14612,7 +14621,7 @@
         <v>1047.04</v>
       </c>
       <c r="G130" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A130=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B130)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A130&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A130=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B130)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H130" s="26" t="n">
@@ -14658,7 +14667,7 @@
         <v>1053.79</v>
       </c>
       <c r="G131" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A131=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B131)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A131&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A131=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B131)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H131" s="26" t="n">
@@ -14704,7 +14713,7 @@
         <v>1060.58</v>
       </c>
       <c r="G132" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A132=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B132)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A132&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A132=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B132)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H132" s="26" t="n">
@@ -14750,7 +14759,7 @@
         <v>1067.41</v>
       </c>
       <c r="G133" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A133=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B133)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A133&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A133=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B133)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H133" s="26" t="n">
@@ -14796,7 +14805,7 @@
         <v>1074.28</v>
       </c>
       <c r="G134" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A134=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B134)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A134&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A134=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B134)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H134" s="26" t="n">
@@ -14842,7 +14851,7 @@
         <v>1081.18</v>
       </c>
       <c r="G135" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A135=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B135)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A135&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A135=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B135)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H135" s="26" t="n">
@@ -14888,7 +14897,7 @@
         <v>1088.12</v>
       </c>
       <c r="G136" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A136=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B136)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A136&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A136=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B136)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H136" s="26" t="n">
@@ -14934,7 +14943,7 @@
         <v>1095.09</v>
       </c>
       <c r="G137" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A137=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B137)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A137&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A137=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B137)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H137" s="26" t="n">
@@ -14980,7 +14989,7 @@
         <v>1102.11</v>
       </c>
       <c r="G138" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A138=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B138)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A138&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A138=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B138)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H138" s="26" t="n">
@@ -15026,7 +15035,7 @@
         <v>1109.16</v>
       </c>
       <c r="G139" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A139=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B139)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A139&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A139=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B139)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H139" s="26" t="n">
@@ -15072,7 +15081,7 @@
         <v>1116.25</v>
       </c>
       <c r="G140" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A140=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B140)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A140&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A140=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B140)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H140" s="26" t="n">
@@ -15118,7 +15127,7 @@
         <v>1128.8</v>
       </c>
       <c r="G141" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A141=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B141)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A141&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A141=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B141)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H141" s="26" t="n">
@@ -15164,7 +15173,7 @@
         <v>1136</v>
       </c>
       <c r="G142" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A142=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B142)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A142&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A142=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B142)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H142" s="26" t="n">
@@ -15210,7 +15219,7 @@
         <v>1143.23</v>
       </c>
       <c r="G143" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A143=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B143)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A143&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A143=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B143)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H143" s="26" t="n">
@@ -15256,7 +15265,7 @@
         <v>1150.51</v>
       </c>
       <c r="G144" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A144=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B144)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A144&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A144=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B144)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H144" s="26" t="n">
@@ -15302,7 +15311,7 @@
         <v>1157.83</v>
       </c>
       <c r="G145" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A145=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B145)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A145&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A145=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B145)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H145" s="26" t="n">
@@ -15348,7 +15357,7 @@
         <v>1165.18</v>
       </c>
       <c r="G146" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A146=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B146)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A146&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A146=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B146)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H146" s="26" t="n">
@@ -15394,7 +15403,7 @@
         <v>1172.58</v>
       </c>
       <c r="G147" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A147=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B147)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A147&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A147=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B147)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H147" s="26" t="n">
@@ -15440,7 +15449,7 @@
         <v>1180.01</v>
       </c>
       <c r="G148" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A148=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B148)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A148&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A148=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B148)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H148" s="26" t="n">
@@ -15486,7 +15495,7 @@
         <v>1187.49</v>
       </c>
       <c r="G149" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A149=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B149)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A149&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A149=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B149)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H149" s="26" t="n">
@@ -15532,7 +15541,7 @@
         <v>1195</v>
       </c>
       <c r="G150" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A150=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B150)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A150&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A150=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B150)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H150" s="26" t="n">
@@ -15578,7 +15587,7 @@
         <v>1202.56</v>
       </c>
       <c r="G151" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A151=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B151)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A151&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A151=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B151)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H151" s="26" t="n">
@@ -15624,7 +15633,7 @@
         <v>1210.15</v>
       </c>
       <c r="G152" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A152=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B152)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A152&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A152=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B152)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H152" s="26" t="n">
@@ -15670,7 +15679,7 @@
         <v>1223.21</v>
       </c>
       <c r="G153" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A153=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B153)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A153&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A153=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B153)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H153" s="26" t="n">
@@ -15716,7 +15725,7 @@
         <v>1230.92</v>
       </c>
       <c r="G154" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A154=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B154)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A154&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A154=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B154)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H154" s="26" t="n">
@@ -15762,7 +15771,7 @@
         <v>1238.67</v>
       </c>
       <c r="G155" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A155=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B155)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A155&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A155=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B155)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H155" s="26" t="n">
@@ -15808,7 +15817,7 @@
         <v>1246.46</v>
       </c>
       <c r="G156" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A156=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B156)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A156&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A156=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B156)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H156" s="26" t="n">
@@ -15854,7 +15863,7 @@
         <v>1254.3</v>
       </c>
       <c r="G157" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A157=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B157)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A157&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A157=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B157)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H157" s="26" t="n">
@@ -15900,7 +15909,7 @@
         <v>1262.17</v>
       </c>
       <c r="G158" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A158=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B158)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A158&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A158=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B158)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H158" s="26" t="n">
@@ -15946,7 +15955,7 @@
         <v>1270.09</v>
       </c>
       <c r="G159" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A159=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B159)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A159&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A159=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B159)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H159" s="26" t="n">
@@ -15992,7 +16001,7 @@
         <v>1278.06</v>
       </c>
       <c r="G160" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A160=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B160)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A160&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A160=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B160)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H160" s="26" t="n">
@@ -16038,7 +16047,7 @@
         <v>1286.06</v>
       </c>
       <c r="G161" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A161=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B161)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A161&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A161=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B161)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H161" s="26" t="n">
@@ -16084,7 +16093,7 @@
         <v>1294.11</v>
       </c>
       <c r="G162" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A162=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B162)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A162&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A162=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B162)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H162" s="26" t="n">
@@ -16130,7 +16139,7 @@
         <v>1302.21</v>
       </c>
       <c r="G163" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A163=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B163)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A163&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A163=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B163)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H163" s="26" t="n">
@@ -16176,7 +16185,7 @@
         <v>1310.34</v>
       </c>
       <c r="G164" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A164=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B164)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A164&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A164=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B164)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H164" s="26" t="n">
@@ -16222,7 +16231,7 @@
         <v>1323.94</v>
       </c>
       <c r="G165" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A165=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B165)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A165&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A165=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B165)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H165" s="26" t="n">
@@ -16268,7 +16277,7 @@
         <v>1332.2</v>
       </c>
       <c r="G166" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A166=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B166)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A166&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A166=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B166)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H166" s="26" t="n">
@@ -16314,7 +16323,7 @@
         <v>1340.5</v>
       </c>
       <c r="G167" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A167=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B167)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A167&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A167=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B167)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H167" s="26" t="n">
@@ -16360,7 +16369,7 @@
         <v>1348.84</v>
       </c>
       <c r="G168" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A168=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B168)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A168&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A168=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B168)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H168" s="26" t="n">
@@ -16406,7 +16415,7 @@
         <v>1357.23</v>
       </c>
       <c r="G169" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A169=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B169)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A169&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A169=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B169)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H169" s="26" t="n">
@@ -16452,7 +16461,7 @@
         <v>1365.66</v>
       </c>
       <c r="G170" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A170=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B170)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A170&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A170=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B170)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H170" s="26" t="n">
@@ -16498,7 +16507,7 @@
         <v>1374.14</v>
       </c>
       <c r="G171" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A171=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B171)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A171&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A171=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B171)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H171" s="26" t="n">
@@ -16544,7 +16553,7 @@
         <v>1382.67</v>
       </c>
       <c r="G172" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A172=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B172)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A172&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A172=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B172)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H172" s="26" t="n">
@@ -16590,7 +16599,7 @@
         <v>1391.24</v>
       </c>
       <c r="G173" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A173=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B173)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A173&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A173=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B173)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H173" s="26" t="n">
@@ -16636,7 +16645,7 @@
         <v>1399.86</v>
       </c>
       <c r="G174" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A174=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B174)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A174&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A174=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B174)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H174" s="26" t="n">
@@ -16682,7 +16691,7 @@
         <v>1408.53</v>
       </c>
       <c r="G175" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A175=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B175)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A175&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A175=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B175)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H175" s="26" t="n">
@@ -16728,7 +16737,7 @@
         <v>1417.24</v>
       </c>
       <c r="G176" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A176=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B176)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A176&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A176=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B176)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H176" s="26" t="n">
@@ -16774,7 +16783,7 @@
         <v>1431.42</v>
       </c>
       <c r="G177" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A177=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B177)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A177&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A177=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B177)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H177" s="26" t="n">
@@ -16820,7 +16829,7 @@
         <v>1440.26</v>
       </c>
       <c r="G178" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A178=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B178)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A178&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A178=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B178)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H178" s="26" t="n">
@@ -16866,7 +16875,7 @@
         <v>1449.14</v>
       </c>
       <c r="G179" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A179=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B179)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A179&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A179=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B179)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H179" s="26" t="n">
@@ -16912,7 +16921,7 @@
         <v>1458.07</v>
       </c>
       <c r="G180" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A180=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B180)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A180&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A180=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B180)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H180" s="26" t="n">
@@ -16958,7 +16967,7 @@
         <v>1467.05</v>
       </c>
       <c r="G181" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A181=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B181)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A181&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A181=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B181)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H181" s="26" t="n">
@@ -17004,7 +17013,7 @@
         <v>1476.08</v>
       </c>
       <c r="G182" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A182=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B182)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A182&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A182=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B182)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H182" s="26" t="n">
@@ -17050,7 +17059,7 @@
         <v>1485.16</v>
       </c>
       <c r="G183" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A183=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B183)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A183&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A183=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B183)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H183" s="26" t="n">
@@ -17096,7 +17105,7 @@
         <v>1494.29</v>
       </c>
       <c r="G184" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A184=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B184)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A184&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A184=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B184)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H184" s="26" t="n">
@@ -17142,7 +17151,7 @@
         <v>1503.47</v>
       </c>
       <c r="G185" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A185=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B185)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A185&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A185=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B185)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H185" s="26" t="n">
@@ -17188,7 +17197,7 @@
         <v>1512.7</v>
       </c>
       <c r="G186" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A186=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B186)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A186&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A186=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B186)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H186" s="26" t="n">
@@ -17234,7 +17243,7 @@
         <v>1521.97</v>
       </c>
       <c r="G187" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A187=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B187)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A187&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A187=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B187)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H187" s="26" t="n">
@@ -17280,7 +17289,7 @@
         <v>1531.3</v>
       </c>
       <c r="G188" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A188=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B188)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A188&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A188=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B188)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H188" s="26" t="n">
@@ -17326,7 +17335,7 @@
         <v>1546.09</v>
       </c>
       <c r="G189" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A189=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B189)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A189&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A189=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B189)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H189" s="26" t="n">
@@ -17372,7 +17381,7 @@
         <v>1555.55</v>
       </c>
       <c r="G190" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A190=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B190)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A190&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A190=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B190)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H190" s="26" t="n">
@@ -17418,7 +17427,7 @@
         <v>1565.06</v>
       </c>
       <c r="G191" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A191=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B191)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A191&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A191=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B191)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H191" s="26" t="n">
@@ -17464,7 +17473,7 @@
         <v>1574.62</v>
       </c>
       <c r="G192" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A192=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B192)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A192&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A192=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B192)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H192" s="26" t="n">
@@ -17510,7 +17519,7 @@
         <v>1584.24</v>
       </c>
       <c r="G193" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A193=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B193)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A193&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A193=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B193)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H193" s="26" t="n">
@@ -17556,7 +17565,7 @@
         <v>1593.9</v>
       </c>
       <c r="G194" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A194=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B194)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A194&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A194=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B194)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H194" s="26" t="n">
@@ -17602,7 +17611,7 @@
         <v>1603.62</v>
       </c>
       <c r="G195" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A195=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B195)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A195&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A195=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B195)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H195" s="26" t="n">
@@ -17648,7 +17657,7 @@
         <v>1613.39</v>
       </c>
       <c r="G196" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A196=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B196)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A196&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A196=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B196)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H196" s="26" t="n">
@@ -17694,7 +17703,7 @@
         <v>1623.21</v>
       </c>
       <c r="G197" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A197=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B197)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A197&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A197=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B197)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H197" s="26" t="n">
@@ -17740,7 +17749,7 @@
         <v>1633.08</v>
       </c>
       <c r="G198" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A198=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B198)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A198&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A198=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B198)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H198" s="26" t="n">
@@ -17786,7 +17795,7 @@
         <v>1643.01</v>
       </c>
       <c r="G199" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A199=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B199)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A199&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A199=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B199)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H199" s="26" t="n">
@@ -17832,7 +17841,7 @@
         <v>1653</v>
       </c>
       <c r="G200" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A200=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B200)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A200&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A200=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B200)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H200" s="26" t="n">
@@ -17878,7 +17887,7 @@
         <v>1668.45</v>
       </c>
       <c r="G201" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A201=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B201)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A201&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A201=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B201)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H201" s="26" t="n">
@@ -17924,7 +17933,7 @@
         <v>1678.57</v>
       </c>
       <c r="G202" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A202=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B202)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A202&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A202=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B202)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H202" s="26" t="n">
@@ -17970,7 +17979,7 @@
         <v>1688.75</v>
       </c>
       <c r="G203" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A203=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B203)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A203&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A203=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B203)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H203" s="26" t="n">
@@ -18016,7 +18025,7 @@
         <v>1698.98</v>
       </c>
       <c r="G204" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A204=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B204)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A204&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A204=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B204)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H204" s="26" t="n">
@@ -18062,7 +18071,7 @@
         <v>1709.26</v>
       </c>
       <c r="G205" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A205=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B205)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A205&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A205=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B205)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H205" s="26" t="n">
@@ -18108,7 +18117,7 @@
         <v>1719.61</v>
       </c>
       <c r="G206" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A206=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B206)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A206&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A206=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B206)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H206" s="26" t="n">
@@ -18154,7 +18163,7 @@
         <v>1730</v>
       </c>
       <c r="G207" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A207=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B207)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A207&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A207=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B207)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H207" s="26" t="n">
@@ -18200,7 +18209,7 @@
         <v>1740.46</v>
       </c>
       <c r="G208" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A208=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B208)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A208&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A208=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B208)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H208" s="26" t="n">
@@ -18246,7 +18255,7 @@
         <v>1750.97</v>
       </c>
       <c r="G209" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A209=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B209)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A209&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A209=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B209)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H209" s="26" t="n">
@@ -18292,7 +18301,7 @@
         <v>1761.54</v>
       </c>
       <c r="G210" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A210=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B210)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A210&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A210=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B210)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H210" s="26" t="n">
@@ -18338,7 +18347,7 @@
         <v>1772.16</v>
       </c>
       <c r="G211" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A211=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B211)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A211&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A211=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B211)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H211" s="26" t="n">
@@ -18384,7 +18393,7 @@
         <v>1782.84</v>
       </c>
       <c r="G212" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A212=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B212)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A212&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A212=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B212)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H212" s="26" t="n">
@@ -18430,7 +18439,7 @@
         <v>1799</v>
       </c>
       <c r="G213" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A213=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B213)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A213&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A213=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B213)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H213" s="26" t="n">
@@ -18476,7 +18485,7 @@
         <v>1809.83</v>
       </c>
       <c r="G214" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A214=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B214)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A214&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A214=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B214)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H214" s="26" t="n">
@@ -18522,7 +18531,7 @@
         <v>1820.72</v>
       </c>
       <c r="G215" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A215=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B215)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A215&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A215=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B215)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H215" s="26" t="n">
@@ -18568,7 +18577,7 @@
         <v>1831.66</v>
       </c>
       <c r="G216" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A216=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B216)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A216&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A216=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B216)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H216" s="26" t="n">
@@ -18614,7 +18623,7 @@
         <v>1842.67</v>
       </c>
       <c r="G217" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A217=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B217)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A217&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A217=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B217)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H217" s="26" t="n">
@@ -18660,7 +18669,7 @@
         <v>1853.73</v>
       </c>
       <c r="G218" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A218=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B218)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A218&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A218=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B218)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H218" s="26" t="n">
@@ -18706,7 +18715,7 @@
         <v>1864.85</v>
       </c>
       <c r="G219" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A219=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B219)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A219&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A219=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B219)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H219" s="26" t="n">
@@ -18752,7 +18761,7 @@
         <v>1876.04</v>
       </c>
       <c r="G220" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A220=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B220)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A220&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A220=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B220)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H220" s="26" t="n">
@@ -18798,7 +18807,7 @@
         <v>1887.28</v>
       </c>
       <c r="G221" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A221=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B221)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A221&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A221=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B221)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H221" s="26" t="n">
@@ -18844,7 +18853,7 @@
         <v>1898.59</v>
       </c>
       <c r="G222" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A222=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B222)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A222&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A222=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B222)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H222" s="26" t="n">
@@ -18890,7 +18899,7 @@
         <v>1909.96</v>
       </c>
       <c r="G223" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A223=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B223)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A223&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A223=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B223)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H223" s="26" t="n">
@@ -18936,7 +18945,7 @@
         <v>1921.39</v>
       </c>
       <c r="G224" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A224=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B224)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A224&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A224=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B224)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H224" s="26" t="n">
@@ -18982,7 +18991,7 @@
         <v>1938.29</v>
       </c>
       <c r="G225" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A225=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B225)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A225&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A225=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B225)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H225" s="26" t="n">
@@ -19028,7 +19037,7 @@
         <v>1949.88</v>
       </c>
       <c r="G226" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A226=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B226)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A226&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A226=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B226)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H226" s="26" t="n">
@@ -19074,7 +19083,7 @@
         <v>1961.52</v>
       </c>
       <c r="G227" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A227=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B227)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A227&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A227=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B227)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H227" s="26" t="n">
@@ -19120,7 +19129,7 @@
         <v>1973.23</v>
       </c>
       <c r="G228" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A228=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B228)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A228&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A228=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B228)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H228" s="26" t="n">
@@ -19166,7 +19175,7 @@
         <v>1985</v>
       </c>
       <c r="G229" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A229=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B229)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A229&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A229=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B229)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H229" s="26" t="n">
@@ -19212,7 +19221,7 @@
         <v>1996.84</v>
       </c>
       <c r="G230" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A230=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B230)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A230&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A230=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B230)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H230" s="26" t="n">
@@ -19258,7 +19267,7 @@
         <v>2008.74</v>
       </c>
       <c r="G231" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A231=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B231)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A231&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A231=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B231)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H231" s="26" t="n">
@@ -19304,7 +19313,7 @@
         <v>2020.7</v>
       </c>
       <c r="G232" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A232=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B232)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A232&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A232=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B232)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H232" s="26" t="n">
@@ -19350,7 +19359,7 @@
         <v>2032.73</v>
       </c>
       <c r="G233" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A233=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B233)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A233&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A233=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B233)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H233" s="26" t="n">
@@ -19396,7 +19405,7 @@
         <v>2044.82</v>
       </c>
       <c r="G234" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A234=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B234)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A234&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A234=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B234)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H234" s="26" t="n">
@@ -19442,7 +19451,7 @@
         <v>2056.98</v>
       </c>
       <c r="G235" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A235=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B235)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A235&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A235=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B235)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H235" s="26" t="n">
@@ -19488,7 +19497,7 @@
         <v>2069.21</v>
       </c>
       <c r="G236" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A236=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B236)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A236&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A236=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B236)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H236" s="26" t="n">
@@ -19534,7 +19543,7 @@
         <v>2086.92</v>
       </c>
       <c r="G237" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A237=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B237)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A237&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A237=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B237)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H237" s="26" t="n">
@@ -19580,7 +19589,7 @@
         <v>2099.3</v>
       </c>
       <c r="G238" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A238=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B238)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A238&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A238=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B238)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H238" s="26" t="n">
@@ -19626,7 +19635,7 @@
         <v>2111.76</v>
       </c>
       <c r="G239" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A239=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B239)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A239&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A239=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B239)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H239" s="26" t="n">
@@ -19672,7 +19681,7 @@
         <v>2124.28</v>
       </c>
       <c r="G240" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A240=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B240)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A240&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A240=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B240)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H240" s="26" t="n">
@@ -19718,7 +19727,7 @@
         <v>2136.87</v>
       </c>
       <c r="G241" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A241=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B241)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A241&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A241=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B241)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H241" s="26" t="n">
@@ -19764,7 +19773,7 @@
         <v>2149.53</v>
       </c>
       <c r="G242" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A242=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B242)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A242&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A242=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B242)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H242" s="26" t="n">
@@ -19810,7 +19819,7 @@
         <v>2162.25</v>
       </c>
       <c r="G243" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A243=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B243)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A243&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A243=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B243)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H243" s="26" t="n">
@@ -19856,7 +19865,7 @@
         <v>2175.05</v>
       </c>
       <c r="G244" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A244=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B244)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A244&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A244=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B244)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H244" s="26" t="n">
@@ -19902,7 +19911,7 @@
         <v>2187.92</v>
       </c>
       <c r="G245" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A245=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B245)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A245&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A245=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B245)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H245" s="26" t="n">
@@ -19948,7 +19957,7 @@
         <v>2200.85</v>
       </c>
       <c r="G246" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A246=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B246)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A246&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A246=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B246)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H246" s="26" t="n">
@@ -19994,7 +20003,7 @@
         <v>2213.85</v>
       </c>
       <c r="G247" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A247=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B247)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A247&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A247=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B247)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H247" s="26" t="n">
@@ -20040,7 +20049,7 @@
         <v>2226.93</v>
       </c>
       <c r="G248" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A248=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B248)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A248&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A248=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B248)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H248" s="26" t="n">
@@ -20086,7 +20095,7 @@
         <v>2245.49</v>
       </c>
       <c r="G249" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A249=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B249)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A249&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A249=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B249)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H249" s="26" t="n">
@@ -20132,7 +20141,7 @@
         <v>2258.74</v>
       </c>
       <c r="G250" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A250=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B250)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A250&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A250=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B250)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H250" s="26" t="n">
@@ -20178,7 +20187,7 @@
         <v>2272.06</v>
       </c>
       <c r="G251" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A251=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B251)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A251&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A251=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B251)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H251" s="26" t="n">
@@ -20224,7 +20233,7 @@
         <v>2285.45</v>
       </c>
       <c r="G252" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A252=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B252)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A252&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A252=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B252)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H252" s="26" t="n">
@@ -20270,7 +20279,7 @@
         <v>2298.91</v>
       </c>
       <c r="G253" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A253=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B253)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A253&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A253=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B253)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H253" s="26" t="n">
@@ -20316,7 +20325,7 @@
         <v>2312.45</v>
       </c>
       <c r="G254" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A254=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B254)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A254&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A254=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B254)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H254" s="26" t="n">
@@ -20362,7 +20371,7 @@
         <v>2326.05</v>
       </c>
       <c r="G255" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A255=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B255)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A255&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A255=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B255)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H255" s="26" t="n">
@@ -20408,7 +20417,7 @@
         <v>2339.74</v>
       </c>
       <c r="G256" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A256=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B256)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A256&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A256=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B256)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H256" s="26" t="n">
@@ -20454,7 +20463,7 @@
         <v>2353.49</v>
       </c>
       <c r="G257" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A257=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B257)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A257&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A257=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B257)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H257" s="26" t="n">
@@ -20500,7 +20509,7 @@
         <v>2367.33</v>
       </c>
       <c r="G258" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A258=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B258)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A258&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A258=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B258)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H258" s="26" t="n">
@@ -20546,7 +20555,7 @@
         <v>2381.23</v>
       </c>
       <c r="G259" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A259=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B259)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A259&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A259=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B259)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H259" s="26" t="n">
@@ -20592,7 +20601,7 @@
         <v>2395.21</v>
       </c>
       <c r="G260" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A260=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B260)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A260&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A260=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B260)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H260" s="26" t="n">
@@ -20638,7 +20647,7 @@
         <v>2414.69</v>
       </c>
       <c r="G261" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A261=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B261)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A261&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A261=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B261)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H261" s="26" t="n">
@@ -20684,7 +20693,7 @@
         <v>2428.85</v>
       </c>
       <c r="G262" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A262=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B262)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A262&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A262=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B262)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H262" s="26" t="n">
@@ -20730,7 +20739,7 @@
         <v>2443.09</v>
       </c>
       <c r="G263" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A263=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B263)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A263&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A263=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B263)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H263" s="26" t="n">
@@ -20776,7 +20785,7 @@
         <v>2457.41</v>
       </c>
       <c r="G264" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A264=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B264)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A264&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A264=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B264)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H264" s="26" t="n">
@@ -20822,7 +20831,7 @@
         <v>2471.8</v>
       </c>
       <c r="G265" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A265=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B265)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A265&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A265=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B265)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H265" s="26" t="n">
@@ -20868,7 +20877,7 @@
         <v>2486.27</v>
       </c>
       <c r="G266" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A266=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B266)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A266&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A266=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B266)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H266" s="26" t="n">
@@ -20914,7 +20923,7 @@
         <v>2500.82</v>
       </c>
       <c r="G267" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A267=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B267)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A267&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A267=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B267)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H267" s="26" t="n">
@@ -20960,7 +20969,7 @@
         <v>2515.45</v>
       </c>
       <c r="G268" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A268=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B268)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A268&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A268=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B268)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H268" s="26" t="n">
@@ -21006,7 +21015,7 @@
         <v>2530.16</v>
       </c>
       <c r="G269" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A269=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B269)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A269&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A269=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B269)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H269" s="26" t="n">
@@ -21052,7 +21061,7 @@
         <v>2544.95</v>
       </c>
       <c r="G270" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A270=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B270)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A270&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A270=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B270)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H270" s="26" t="n">
@@ -21098,7 +21107,7 @@
         <v>2559.82</v>
       </c>
       <c r="G271" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A271=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B271)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A271&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A271=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B271)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H271" s="26" t="n">
@@ -21144,7 +21153,7 @@
         <v>2574.77</v>
       </c>
       <c r="G272" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A272=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B272)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A272&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A272=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B272)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H272" s="26" t="n">
@@ -21190,7 +21199,7 @@
         <v>2595.21</v>
       </c>
       <c r="G273" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A273=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B273)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A273&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A273=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B273)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H273" s="26" t="n">
@@ -21236,7 +21245,7 @@
         <v>2610.36</v>
       </c>
       <c r="G274" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A274=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B274)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A274&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A274=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B274)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H274" s="26" t="n">
@@ -21282,7 +21291,7 @@
         <v>2625.58</v>
       </c>
       <c r="G275" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A275=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B275)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A275&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A275=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B275)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H275" s="26" t="n">
@@ -21328,7 +21337,7 @@
         <v>2548.86</v>
       </c>
       <c r="G276" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A276=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B276)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A276&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A276=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B276)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H276" s="26" t="n">
@@ -21374,7 +21383,7 @@
         <v>0</v>
       </c>
       <c r="G277" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A277=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B277)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A277&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A277=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B277)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H277" s="26" t="n">
@@ -21420,7 +21429,7 @@
         <v>0</v>
       </c>
       <c r="G278" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A278=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B278)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A278&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A278=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B278)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H278" s="26" t="n">
@@ -21466,7 +21475,7 @@
         <v>0</v>
       </c>
       <c r="G279" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A279=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B279)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A279&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A279=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B279)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H279" s="26" t="n">
@@ -21512,7 +21521,7 @@
         <v>0</v>
       </c>
       <c r="G280" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A280=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B280)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A280&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A280=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B280)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H280" s="26" t="n">
@@ -21558,7 +21567,7 @@
         <v>0</v>
       </c>
       <c r="G281" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A281=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B281)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A281&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A281=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B281)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H281" s="26" t="n">
@@ -21604,7 +21613,7 @@
         <v>0</v>
       </c>
       <c r="G282" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A282=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B282)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A282&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A282=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B282)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H282" s="26" t="n">
@@ -21650,7 +21659,7 @@
         <v>0</v>
       </c>
       <c r="G283" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A283=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B283)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A283&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A283=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B283)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H283" s="26" t="n">
@@ -21696,7 +21705,7 @@
         <v>0</v>
       </c>
       <c r="G284" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A284=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B284)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A284&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A284=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B284)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H284" s="26" t="n">
@@ -21742,7 +21751,7 @@
         <v>0</v>
       </c>
       <c r="G285" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A285=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B285)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A285&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A285=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B285)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H285" s="26" t="n">
@@ -21788,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="G286" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A286=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B286)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A286&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A286=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B286)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H286" s="26" t="n">
@@ -21834,7 +21843,7 @@
         <v>0</v>
       </c>
       <c r="G287" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A287=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B287)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A287&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A287=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B287)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H287" s="26" t="n">
@@ -21880,7 +21889,7 @@
         <v>0</v>
       </c>
       <c r="G288" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A288=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B288)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A288&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A288=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B288)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H288" s="26" t="n">
@@ -21926,7 +21935,7 @@
         <v>0</v>
       </c>
       <c r="G289" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A289=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B289)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A289&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A289=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B289)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H289" s="26" t="n">
@@ -21972,7 +21981,7 @@
         <v>0</v>
       </c>
       <c r="G290" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A290=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B290)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A290&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A290=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B290)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H290" s="26" t="n">
@@ -22018,7 +22027,7 @@
         <v>0</v>
       </c>
       <c r="G291" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A291=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B291)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A291&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A291=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B291)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H291" s="26" t="n">
@@ -22064,7 +22073,7 @@
         <v>0</v>
       </c>
       <c r="G292" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A292=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B292)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A292&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A292=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B292)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H292" s="26" t="n">
@@ -22110,7 +22119,7 @@
         <v>0</v>
       </c>
       <c r="G293" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A293=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B293)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A293&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A293=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B293)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H293" s="26" t="n">
@@ -22156,7 +22165,7 @@
         <v>0</v>
       </c>
       <c r="G294" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A294=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B294)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A294&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A294=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B294)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H294" s="26" t="n">
@@ -22202,7 +22211,7 @@
         <v>0</v>
       </c>
       <c r="G295" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A295=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B295)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A295&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A295=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B295)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H295" s="26" t="n">
@@ -22248,7 +22257,7 @@
         <v>0</v>
       </c>
       <c r="G296" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A296=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B296)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A296&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A296=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B296)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H296" s="26" t="n">
@@ -22294,7 +22303,7 @@
         <v>0</v>
       </c>
       <c r="G297" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A297=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B297)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A297&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A297=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B297)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H297" s="26" t="n">
@@ -22340,7 +22349,7 @@
         <v>0</v>
       </c>
       <c r="G298" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A298=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B298)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A298&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A298=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B298)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H298" s="26" t="n">
@@ -22386,7 +22395,7 @@
         <v>0</v>
       </c>
       <c r="G299" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A299=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B299)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A299&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A299=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B299)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H299" s="26" t="n">
@@ -22432,7 +22441,7 @@
         <v>0</v>
       </c>
       <c r="G300" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A300=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B300)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A300&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A300=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B300)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H300" s="26" t="n">
@@ -22478,7 +22487,7 @@
         <v>0</v>
       </c>
       <c r="G301" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A301=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B301)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A301&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A301=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B301)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H301" s="26" t="n">
@@ -22524,7 +22533,7 @@
         <v>0</v>
       </c>
       <c r="G302" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A302=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B302)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A302&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A302=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B302)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H302" s="26" t="n">
@@ -22570,7 +22579,7 @@
         <v>0</v>
       </c>
       <c r="G303" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A303=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B303)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A303&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A303=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B303)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H303" s="26" t="n">
@@ -22616,7 +22625,7 @@
         <v>0</v>
       </c>
       <c r="G304" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A304=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B304)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A304&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A304=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B304)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H304" s="26" t="n">
@@ -22662,7 +22671,7 @@
         <v>0</v>
       </c>
       <c r="G305" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A305=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B305)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A305&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A305=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B305)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H305" s="26" t="n">
@@ -22708,7 +22717,7 @@
         <v>0</v>
       </c>
       <c r="G306" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A306=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B306)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A306&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A306=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B306)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H306" s="26" t="n">
@@ -22754,7 +22763,7 @@
         <v>0</v>
       </c>
       <c r="G307" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A307=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B307)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A307&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A307=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B307)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H307" s="26" t="n">
@@ -22800,7 +22809,7 @@
         <v>0</v>
       </c>
       <c r="G308" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A308=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B308)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A308&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A308=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B308)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H308" s="26" t="n">
@@ -22846,7 +22855,7 @@
         <v>0</v>
       </c>
       <c r="G309" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A309=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B309)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A309&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A309=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B309)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H309" s="26" t="n">
@@ -22892,7 +22901,7 @@
         <v>0</v>
       </c>
       <c r="G310" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A310=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B310)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A310&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A310=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B310)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H310" s="26" t="n">
@@ -22938,7 +22947,7 @@
         <v>0</v>
       </c>
       <c r="G311" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A311=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B311)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A311&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A311=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B311)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H311" s="26" t="n">
@@ -22984,7 +22993,7 @@
         <v>0</v>
       </c>
       <c r="G312" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A312=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B312)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A312&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A312=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B312)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H312" s="26" t="n">
@@ -23030,7 +23039,7 @@
         <v>0</v>
       </c>
       <c r="G313" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A313=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B313)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A313&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A313=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B313)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H313" s="26" t="n">
@@ -23076,7 +23085,7 @@
         <v>0</v>
       </c>
       <c r="G314" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A314=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B314)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A314&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A314=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B314)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H314" s="26" t="n">
@@ -23122,7 +23131,7 @@
         <v>0</v>
       </c>
       <c r="G315" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A315=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B315)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A315&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A315=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B315)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H315" s="26" t="n">
@@ -23168,7 +23177,7 @@
         <v>0</v>
       </c>
       <c r="G316" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A316=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B316)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A316&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A316=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B316)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H316" s="26" t="n">
@@ -23214,7 +23223,7 @@
         <v>0</v>
       </c>
       <c r="G317" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A317=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B317)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A317&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A317=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B317)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H317" s="26" t="n">
@@ -23260,7 +23269,7 @@
         <v>0</v>
       </c>
       <c r="G318" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A318=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B318)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A318&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A318=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B318)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H318" s="26" t="n">
@@ -23306,7 +23315,7 @@
         <v>0</v>
       </c>
       <c r="G319" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A319=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B319)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A319&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A319=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B319)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H319" s="26" t="n">
@@ -23352,7 +23361,7 @@
         <v>0</v>
       </c>
       <c r="G320" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A320=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B320)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A320&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A320=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B320)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H320" s="26" t="n">
@@ -23398,7 +23407,7 @@
         <v>0</v>
       </c>
       <c r="G321" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A321=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B321)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A321&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A321=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B321)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H321" s="26" t="n">
@@ -23444,7 +23453,7 @@
         <v>0</v>
       </c>
       <c r="G322" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A322=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B322)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A322&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A322=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B322)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H322" s="26" t="n">
@@ -23490,7 +23499,7 @@
         <v>0</v>
       </c>
       <c r="G323" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A323=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B323)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A323&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A323=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B323)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H323" s="26" t="n">
@@ -23536,7 +23545,7 @@
         <v>0</v>
       </c>
       <c r="G324" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A324=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B324)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A324&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A324=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B324)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H324" s="26" t="n">
@@ -23582,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="G325" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A325=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B325)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A325&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A325=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B325)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H325" s="26" t="n">
@@ -23628,7 +23637,7 @@
         <v>0</v>
       </c>
       <c r="G326" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A326=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B326)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A326&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A326=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B326)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H326" s="26" t="n">
@@ -23674,7 +23683,7 @@
         <v>0</v>
       </c>
       <c r="G327" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A327=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B327)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A327&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A327=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B327)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H327" s="26" t="n">
@@ -23720,7 +23729,7 @@
         <v>0</v>
       </c>
       <c r="G328" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A328=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B328)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A328&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A328=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B328)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H328" s="26" t="n">
@@ -23766,7 +23775,7 @@
         <v>0</v>
       </c>
       <c r="G329" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A329=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B329)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A329&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A329=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B329)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H329" s="26" t="n">
@@ -23812,7 +23821,7 @@
         <v>0</v>
       </c>
       <c r="G330" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A330=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B330)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A330&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A330=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B330)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H330" s="26" t="n">
@@ -23858,7 +23867,7 @@
         <v>0</v>
       </c>
       <c r="G331" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A331=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B331)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A331&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A331=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B331)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H331" s="26" t="n">
@@ -23904,7 +23913,7 @@
         <v>0</v>
       </c>
       <c r="G332" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A332=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B332)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A332&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A332=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B332)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H332" s="26" t="n">
@@ -23950,7 +23959,7 @@
         <v>0</v>
       </c>
       <c r="G333" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A333=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B333)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A333&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A333=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B333)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H333" s="26" t="n">
@@ -23996,7 +24005,7 @@
         <v>0</v>
       </c>
       <c r="G334" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A334=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B334)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A334&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A334=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B334)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H334" s="26" t="n">
@@ -24042,7 +24051,7 @@
         <v>0</v>
       </c>
       <c r="G335" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A335=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B335)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A335&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A335=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B335)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H335" s="26" t="n">
@@ -24088,7 +24097,7 @@
         <v>0</v>
       </c>
       <c r="G336" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A336=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B336)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A336&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A336=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B336)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H336" s="26" t="n">
@@ -24134,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="G337" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A337=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B337)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A337&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A337=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B337)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H337" s="26" t="n">
@@ -24180,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="G338" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A338=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B338)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A338&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A338=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B338)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H338" s="26" t="n">
@@ -24226,7 +24235,7 @@
         <v>0</v>
       </c>
       <c r="G339" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A339=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B339)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A339&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A339=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B339)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H339" s="26" t="n">
@@ -24272,7 +24281,7 @@
         <v>0</v>
       </c>
       <c r="G340" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A340=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B340)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A340&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A340=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B340)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H340" s="26" t="n">
@@ -24318,7 +24327,7 @@
         <v>0</v>
       </c>
       <c r="G341" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A341=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B341)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A341&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A341=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B341)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H341" s="26" t="n">
@@ -24364,7 +24373,7 @@
         <v>0</v>
       </c>
       <c r="G342" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A342=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B342)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A342&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A342=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B342)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H342" s="26" t="n">
@@ -24410,7 +24419,7 @@
         <v>0</v>
       </c>
       <c r="G343" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A343=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B343)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A343&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A343=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B343)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H343" s="26" t="n">
@@ -24456,7 +24465,7 @@
         <v>0</v>
       </c>
       <c r="G344" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A344=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B344)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A344&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A344=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B344)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H344" s="26" t="n">
@@ -24502,7 +24511,7 @@
         <v>0</v>
       </c>
       <c r="G345" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A345=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B345)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A345&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A345=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B345)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H345" s="26" t="n">
@@ -24548,7 +24557,7 @@
         <v>0</v>
       </c>
       <c r="G346" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A346=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B346)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A346&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A346=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B346)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H346" s="26" t="n">
@@ -24594,7 +24603,7 @@
         <v>0</v>
       </c>
       <c r="G347" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A347=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B347)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A347&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A347=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B347)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H347" s="26" t="n">
@@ -24640,7 +24649,7 @@
         <v>0</v>
       </c>
       <c r="G348" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A348=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B348)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A348&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A348=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B348)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H348" s="26" t="n">
@@ -24686,7 +24695,7 @@
         <v>0</v>
       </c>
       <c r="G349" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A349=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B349)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A349&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A349=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B349)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H349" s="26" t="n">
@@ -24732,7 +24741,7 @@
         <v>0</v>
       </c>
       <c r="G350" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A350=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B350)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A350&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A350=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B350)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H350" s="26" t="n">
@@ -24778,7 +24787,7 @@
         <v>0</v>
       </c>
       <c r="G351" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A351=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B351)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A351&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A351=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B351)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H351" s="26" t="n">
@@ -24824,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="G352" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A352=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B352)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A352&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A352=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B352)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H352" s="26" t="n">
@@ -24870,7 +24879,7 @@
         <v>0</v>
       </c>
       <c r="G353" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A353=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B353)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A353&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A353=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B353)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H353" s="26" t="n">
@@ -24916,7 +24925,7 @@
         <v>0</v>
       </c>
       <c r="G354" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A354=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B354)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A354&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A354=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B354)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H354" s="26" t="n">
@@ -24962,7 +24971,7 @@
         <v>0</v>
       </c>
       <c r="G355" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A355=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B355)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A355&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A355=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B355)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H355" s="26" t="n">
@@ -25008,7 +25017,7 @@
         <v>0</v>
       </c>
       <c r="G356" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A356=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B356)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A356&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A356=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B356)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H356" s="26" t="n">
@@ -25054,7 +25063,7 @@
         <v>0</v>
       </c>
       <c r="G357" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A357=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B357)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A357&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A357=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B357)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H357" s="26" t="n">
@@ -25100,7 +25109,7 @@
         <v>0</v>
       </c>
       <c r="G358" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A358=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B358)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A358&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A358=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B358)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H358" s="26" t="n">
@@ -25146,7 +25155,7 @@
         <v>0</v>
       </c>
       <c r="G359" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A359=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B359)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A359&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A359=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B359)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H359" s="26" t="n">
@@ -25192,7 +25201,7 @@
         <v>0</v>
       </c>
       <c r="G360" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A360=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B360)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A360&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A360=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B360)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H360" s="26" t="n">
@@ -25238,7 +25247,7 @@
         <v>0</v>
       </c>
       <c r="G361" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A361=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B361)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A361&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A361=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B361)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H361" s="26" t="n">
@@ -25284,7 +25293,7 @@
         <v>0</v>
       </c>
       <c r="G362" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A362=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B362)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A362&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A362=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B362)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H362" s="26" t="n">
@@ -25330,7 +25339,7 @@
         <v>0</v>
       </c>
       <c r="G363" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A363=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B363)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A363&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A363=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B363)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H363" s="26" t="n">
@@ -25376,7 +25385,7 @@
         <v>0</v>
       </c>
       <c r="G364" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A364=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B364)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A364&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A364=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B364)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H364" s="26" t="n">
@@ -25422,7 +25431,7 @@
         <v>0</v>
       </c>
       <c r="G365" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A365=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B365)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A365&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A365=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B365)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H365" s="26" t="n">
@@ -25468,7 +25477,7 @@
         <v>0</v>
       </c>
       <c r="G366" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A366=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B366)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A366&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A366=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B366)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H366" s="26" t="n">
@@ -25514,7 +25523,7 @@
         <v>0</v>
       </c>
       <c r="G367" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A367=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B367)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A367&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A367=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B367)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H367" s="26" t="n">
@@ -25560,7 +25569,7 @@
         <v>0</v>
       </c>
       <c r="G368" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A368=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B368)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A368&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A368=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B368)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H368" s="26" t="n">
@@ -25606,7 +25615,7 @@
         <v>0</v>
       </c>
       <c r="G369" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A369=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B369)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A369&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A369=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B369)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H369" s="26" t="n">
@@ -25652,7 +25661,7 @@
         <v>0</v>
       </c>
       <c r="G370" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A370=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B370)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A370&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A370=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B370)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H370" s="26" t="n">
@@ -25698,7 +25707,7 @@
         <v>0</v>
       </c>
       <c r="G371" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A371=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B371)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A371&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A371=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B371)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H371" s="26" t="n">
@@ -25744,7 +25753,7 @@
         <v>0</v>
       </c>
       <c r="G372" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A372=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B372)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A372&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A372=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B372)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H372" s="26" t="n">
@@ -25790,7 +25799,7 @@
         <v>0</v>
       </c>
       <c r="G373" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A373=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B373)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A373&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A373=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B373)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H373" s="26" t="n">
@@ -25836,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G374" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A374=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B374)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A374&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A374=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B374)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H374" s="26" t="n">
@@ -25882,7 +25891,7 @@
         <v>0</v>
       </c>
       <c r="G375" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A375=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B375)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A375&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A375=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B375)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H375" s="26" t="n">
@@ -25928,7 +25937,7 @@
         <v>0</v>
       </c>
       <c r="G376" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A376=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B376)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A376&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A376=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B376)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H376" s="26" t="n">
@@ -25974,7 +25983,7 @@
         <v>0</v>
       </c>
       <c r="G377" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A377=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B377)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A377&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A377=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B377)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H377" s="26" t="n">
@@ -26020,7 +26029,7 @@
         <v>0</v>
       </c>
       <c r="G378" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A378=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B378)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A378&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A378=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B378)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H378" s="26" t="n">
@@ -26066,7 +26075,7 @@
         <v>0</v>
       </c>
       <c r="G379" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A379=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B379)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A379&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A379=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B379)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H379" s="26" t="n">
@@ -26112,7 +26121,7 @@
         <v>0</v>
       </c>
       <c r="G380" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A380=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B380)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A380&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A380=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B380)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H380" s="26" t="n">
@@ -26158,7 +26167,7 @@
         <v>0</v>
       </c>
       <c r="G381" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A381=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B381)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A381&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A381=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B381)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H381" s="26" t="n">
@@ -26204,7 +26213,7 @@
         <v>0</v>
       </c>
       <c r="G382" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A382=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B382)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A382&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A382=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B382)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H382" s="26" t="n">
@@ -26250,7 +26259,7 @@
         <v>0</v>
       </c>
       <c r="G383" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A383=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B383)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A383&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A383=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B383)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H383" s="26" t="n">
@@ -26296,7 +26305,7 @@
         <v>0</v>
       </c>
       <c r="G384" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A384=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B384)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A384&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A384=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B384)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H384" s="26" t="n">
@@ -26342,7 +26351,7 @@
         <v>0</v>
       </c>
       <c r="G385" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A385=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B385)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A385&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A385=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B385)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H385" s="26" t="n">
@@ -26388,7 +26397,7 @@
         <v>0</v>
       </c>
       <c r="G386" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A386=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B386)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A386&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A386=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B386)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H386" s="26" t="n">
@@ -26434,7 +26443,7 @@
         <v>0</v>
       </c>
       <c r="G387" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A387=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B387)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A387&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A387=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B387)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H387" s="26" t="n">
@@ -26480,7 +26489,7 @@
         <v>0</v>
       </c>
       <c r="G388" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A388=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B388)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A388&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A388=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B388)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H388" s="26" t="n">
@@ -26526,7 +26535,7 @@
         <v>0</v>
       </c>
       <c r="G389" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A389=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B389)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A389&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A389=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B389)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H389" s="26" t="n">
@@ -26572,7 +26581,7 @@
         <v>0</v>
       </c>
       <c r="G390" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A390=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B390)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A390&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A390=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B390)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H390" s="26" t="n">
@@ -26618,7 +26627,7 @@
         <v>0</v>
       </c>
       <c r="G391" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A391=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B391)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A391&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A391=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B391)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H391" s="26" t="n">
@@ -26664,7 +26673,7 @@
         <v>0</v>
       </c>
       <c r="G392" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A392=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B392)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A392&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A392=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B392)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H392" s="26" t="n">
@@ -26710,7 +26719,7 @@
         <v>0</v>
       </c>
       <c r="G393" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A393=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B393)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A393&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A393=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B393)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H393" s="26" t="n">
@@ -26756,7 +26765,7 @@
         <v>0</v>
       </c>
       <c r="G394" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A394=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B394)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A394&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A394=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B394)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H394" s="26" t="n">
@@ -26802,7 +26811,7 @@
         <v>0</v>
       </c>
       <c r="G395" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A395=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B395)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A395&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A395=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B395)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H395" s="26" t="n">
@@ -26848,7 +26857,7 @@
         <v>0</v>
       </c>
       <c r="G396" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A396=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B396)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A396&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A396=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B396)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H396" s="26" t="n">
@@ -26894,7 +26903,7 @@
         <v>0</v>
       </c>
       <c r="G397" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A397=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B397)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A397&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A397=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B397)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H397" s="26" t="n">
@@ -26940,7 +26949,7 @@
         <v>0</v>
       </c>
       <c r="G398" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A398=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B398)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A398&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A398=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B398)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H398" s="26" t="n">
@@ -26986,7 +26995,7 @@
         <v>0</v>
       </c>
       <c r="G399" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A399=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B399)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A399&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A399=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B399)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H399" s="26" t="n">
@@ -27032,7 +27041,7 @@
         <v>0</v>
       </c>
       <c r="G400" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A400=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B400)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A400&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A400=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B400)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H400" s="26" t="n">
@@ -27078,7 +27087,7 @@
         <v>0</v>
       </c>
       <c r="G401" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A401=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B401)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A401&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A401=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B401)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H401" s="26" t="n">
@@ -27124,7 +27133,7 @@
         <v>0</v>
       </c>
       <c r="G402" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A402=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B402)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A402&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A402=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B402)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H402" s="26" t="n">
@@ -27170,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="G403" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A403=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B403)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A403&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A403=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B403)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H403" s="26" t="n">
@@ -27216,7 +27225,7 @@
         <v>0</v>
       </c>
       <c r="G404" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A404=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B404)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A404&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A404=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B404)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H404" s="26" t="n">
@@ -27262,7 +27271,7 @@
         <v>0</v>
       </c>
       <c r="G405" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A405=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B405)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A405&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A405=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B405)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H405" s="26" t="n">
@@ -27308,7 +27317,7 @@
         <v>0</v>
       </c>
       <c r="G406" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A406=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B406)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A406&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A406=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B406)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H406" s="26" t="n">
@@ -27354,7 +27363,7 @@
         <v>0</v>
       </c>
       <c r="G407" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A407=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B407)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A407&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A407=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B407)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H407" s="26" t="n">
@@ -27400,7 +27409,7 @@
         <v>0</v>
       </c>
       <c r="G408" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A408=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B408)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A408&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A408=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B408)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H408" s="26" t="n">
@@ -27446,7 +27455,7 @@
         <v>0</v>
       </c>
       <c r="G409" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A409=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B409)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A409&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A409=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B409)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H409" s="26" t="n">
@@ -27492,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="G410" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A410=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B410)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A410&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A410=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B410)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H410" s="26" t="n">
@@ -27538,7 +27547,7 @@
         <v>0</v>
       </c>
       <c r="G411" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A411=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B411)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A411&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A411=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B411)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H411" s="26" t="n">
@@ -27584,7 +27593,7 @@
         <v>0</v>
       </c>
       <c r="G412" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A412=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B412)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A412&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A412=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B412)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H412" s="26" t="n">
@@ -27630,7 +27639,7 @@
         <v>0</v>
       </c>
       <c r="G413" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A413=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B413)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A413&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A413=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B413)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H413" s="26" t="n">
@@ -27676,7 +27685,7 @@
         <v>0</v>
       </c>
       <c r="G414" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A414=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B414)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A414&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A414=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B414)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H414" s="26" t="n">
@@ -27722,7 +27731,7 @@
         <v>0</v>
       </c>
       <c r="G415" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A415=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B415)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A415&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A415=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B415)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H415" s="26" t="n">
@@ -27768,7 +27777,7 @@
         <v>0</v>
       </c>
       <c r="G416" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A416=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B416)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A416&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A416=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B416)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H416" s="26" t="n">
@@ -27814,7 +27823,7 @@
         <v>0</v>
       </c>
       <c r="G417" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A417=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B417)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A417&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A417=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B417)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H417" s="26" t="n">
@@ -27860,7 +27869,7 @@
         <v>0</v>
       </c>
       <c r="G418" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A418=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B418)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A418&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A418=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B418)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H418" s="26" t="n">
@@ -27906,7 +27915,7 @@
         <v>0</v>
       </c>
       <c r="G419" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A419=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B419)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A419&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A419=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B419)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H419" s="26" t="n">
@@ -27952,7 +27961,7 @@
         <v>0</v>
       </c>
       <c r="G420" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A420=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B420)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A420&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A420=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B420)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H420" s="26" t="n">
@@ -27998,7 +28007,7 @@
         <v>0</v>
       </c>
       <c r="G421" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A421=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B421)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A421&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A421=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B421)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H421" s="26" t="n">
@@ -28044,7 +28053,7 @@
         <v>0</v>
       </c>
       <c r="G422" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A422=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B422)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A422&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A422=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B422)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H422" s="26" t="n">
@@ -28090,7 +28099,7 @@
         <v>0</v>
       </c>
       <c r="G423" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A423=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B423)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A423&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A423=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B423)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H423" s="26" t="n">
@@ -28136,7 +28145,7 @@
         <v>0</v>
       </c>
       <c r="G424" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A424=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B424)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A424&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A424=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B424)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H424" s="26" t="n">
@@ -28182,7 +28191,7 @@
         <v>0</v>
       </c>
       <c r="G425" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A425=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B425)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A425&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A425=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B425)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H425" s="26" t="n">
@@ -28228,7 +28237,7 @@
         <v>0</v>
       </c>
       <c r="G426" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A426=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B426)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A426&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A426=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B426)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H426" s="26" t="n">
@@ -28274,7 +28283,7 @@
         <v>0</v>
       </c>
       <c r="G427" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A427=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B427)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A427&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A427=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B427)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H427" s="26" t="n">
@@ -28320,7 +28329,7 @@
         <v>0</v>
       </c>
       <c r="G428" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A428=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B428)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A428&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A428=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B428)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H428" s="26" t="n">
@@ -28366,7 +28375,7 @@
         <v>0</v>
       </c>
       <c r="G429" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A429=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B429)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A429&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A429=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B429)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H429" s="26" t="n">
@@ -28412,7 +28421,7 @@
         <v>0</v>
       </c>
       <c r="G430" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A430=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B430)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A430&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A430=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B430)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H430" s="26" t="n">
@@ -28458,7 +28467,7 @@
         <v>0</v>
       </c>
       <c r="G431" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A431=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B431)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A431&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A431=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B431)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H431" s="26" t="n">
@@ -28504,7 +28513,7 @@
         <v>0</v>
       </c>
       <c r="G432" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A432=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B432)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A432&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A432=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B432)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H432" s="26" t="n">
@@ -28550,7 +28559,7 @@
         <v>0</v>
       </c>
       <c r="G433" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A433=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B433)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A433&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A433=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B433)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H433" s="26" t="n">
@@ -28596,7 +28605,7 @@
         <v>0</v>
       </c>
       <c r="G434" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A434=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B434)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A434&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A434=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B434)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H434" s="26" t="n">
@@ -28642,7 +28651,7 @@
         <v>0</v>
       </c>
       <c r="G435" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A435=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B435)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A435&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A435=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B435)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H435" s="26" t="n">
@@ -28688,7 +28697,7 @@
         <v>0</v>
       </c>
       <c r="G436" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A436=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B436)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A436&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A436=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B436)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H436" s="26" t="n">
@@ -28734,7 +28743,7 @@
         <v>0</v>
       </c>
       <c r="G437" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A437=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B437)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A437&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A437=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B437)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H437" s="26" t="n">
@@ -28780,7 +28789,7 @@
         <v>0</v>
       </c>
       <c r="G438" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A438=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B438)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A438&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A438=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B438)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H438" s="26" t="n">
@@ -28826,7 +28835,7 @@
         <v>0</v>
       </c>
       <c r="G439" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A439=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B439)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A439&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A439=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B439)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H439" s="26" t="n">
@@ -28872,7 +28881,7 @@
         <v>0</v>
       </c>
       <c r="G440" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A440=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B440)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A440&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A440=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B440)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H440" s="26" t="n">
@@ -28918,7 +28927,7 @@
         <v>0</v>
       </c>
       <c r="G441" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A441=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B441)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A441&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A441=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B441)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H441" s="26" t="n">
@@ -28964,7 +28973,7 @@
         <v>0</v>
       </c>
       <c r="G442" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A442=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B442)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A442&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A442=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B442)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H442" s="26" t="n">
@@ -29010,7 +29019,7 @@
         <v>0</v>
       </c>
       <c r="G443" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A443=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B443)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A443&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A443=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B443)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H443" s="26" t="n">
@@ -29056,7 +29065,7 @@
         <v>0</v>
       </c>
       <c r="G444" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A444=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B444)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A444&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A444=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B444)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H444" s="26" t="n">
@@ -29102,7 +29111,7 @@
         <v>0</v>
       </c>
       <c r="G445" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A445=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B445)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A445&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A445=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B445)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H445" s="26" t="n">
@@ -29148,7 +29157,7 @@
         <v>0</v>
       </c>
       <c r="G446" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A446=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B446)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A446&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A446=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B446)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H446" s="26" t="n">
@@ -29194,7 +29203,7 @@
         <v>0</v>
       </c>
       <c r="G447" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A447=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B447)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A447&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A447=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B447)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H447" s="26" t="n">
@@ -29240,7 +29249,7 @@
         <v>0</v>
       </c>
       <c r="G448" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A448=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B448)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A448&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A448=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B448)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H448" s="26" t="n">
@@ -29286,7 +29295,7 @@
         <v>0</v>
       </c>
       <c r="G449" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A449=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B449)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A449&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A449=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B449)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H449" s="26" t="n">
@@ -29332,7 +29341,7 @@
         <v>0</v>
       </c>
       <c r="G450" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A450=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B450)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A450&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A450=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B450)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H450" s="26" t="n">
@@ -29378,7 +29387,7 @@
         <v>0</v>
       </c>
       <c r="G451" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A451=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B451)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A451&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A451=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B451)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H451" s="26" t="n">
@@ -29424,7 +29433,7 @@
         <v>0</v>
       </c>
       <c r="G452" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A452=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B452)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A452&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A452=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B452)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H452" s="26" t="n">
@@ -29470,7 +29479,7 @@
         <v>0</v>
       </c>
       <c r="G453" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A453=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B453)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A453&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A453=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B453)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H453" s="26" t="n">
@@ -29516,7 +29525,7 @@
         <v>0</v>
       </c>
       <c r="G454" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A454=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B454)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A454&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A454=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B454)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H454" s="26" t="n">
@@ -29562,7 +29571,7 @@
         <v>0</v>
       </c>
       <c r="G455" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A455=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B455)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A455&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A455=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B455)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H455" s="26" t="n">
@@ -29608,7 +29617,7 @@
         <v>0</v>
       </c>
       <c r="G456" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A456=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B456)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A456&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A456=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B456)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H456" s="26" t="n">
@@ -29654,7 +29663,7 @@
         <v>0</v>
       </c>
       <c r="G457" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A457=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B457)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A457&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A457=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B457)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H457" s="26" t="n">
@@ -29700,7 +29709,7 @@
         <v>0</v>
       </c>
       <c r="G458" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A458=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B458)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A458&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A458=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B458)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H458" s="26" t="n">
@@ -29746,7 +29755,7 @@
         <v>0</v>
       </c>
       <c r="G459" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A459=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B459)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A459&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A459=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B459)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H459" s="26" t="n">
@@ -29792,7 +29801,7 @@
         <v>0</v>
       </c>
       <c r="G460" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A460=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B460)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A460&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A460=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B460)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H460" s="26" t="n">
@@ -29838,7 +29847,7 @@
         <v>0</v>
       </c>
       <c r="G461" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A461=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B461)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A461&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A461=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B461)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H461" s="26" t="n">
@@ -29884,7 +29893,7 @@
         <v>0</v>
       </c>
       <c r="G462" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A462=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B462)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A462&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A462=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B462)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H462" s="26" t="n">
@@ -29930,7 +29939,7 @@
         <v>0</v>
       </c>
       <c r="G463" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A463=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B463)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A463&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A463=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B463)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H463" s="26" t="n">
@@ -29976,7 +29985,7 @@
         <v>0</v>
       </c>
       <c r="G464" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A464=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B464)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A464&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A464=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B464)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H464" s="26" t="n">
@@ -30022,7 +30031,7 @@
         <v>0</v>
       </c>
       <c r="G465" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A465=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B465)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A465&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A465=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B465)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H465" s="26" t="n">
@@ -30068,7 +30077,7 @@
         <v>0</v>
       </c>
       <c r="G466" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A466=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B466)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A466&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A466=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B466)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H466" s="26" t="n">
@@ -30114,7 +30123,7 @@
         <v>0</v>
       </c>
       <c r="G467" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A467=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B467)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A467&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A467=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B467)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H467" s="26" t="n">
@@ -30160,7 +30169,7 @@
         <v>0</v>
       </c>
       <c r="G468" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A468=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B468)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A468&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A468=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B468)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H468" s="26" t="n">
@@ -30206,7 +30215,7 @@
         <v>0</v>
       </c>
       <c r="G469" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A469=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B469)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A469&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A469=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B469)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H469" s="26" t="n">
@@ -30252,7 +30261,7 @@
         <v>0</v>
       </c>
       <c r="G470" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A470=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B470)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A470&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A470=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B470)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H470" s="26" t="n">
@@ -30298,7 +30307,7 @@
         <v>0</v>
       </c>
       <c r="G471" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A471=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B471)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A471&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A471=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B471)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H471" s="26" t="n">
@@ -30344,7 +30353,7 @@
         <v>0</v>
       </c>
       <c r="G472" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A472=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B472)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A472&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A472=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B472)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H472" s="26" t="n">
@@ -30390,7 +30399,7 @@
         <v>0</v>
       </c>
       <c r="G473" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A473=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B473)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A473&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A473=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B473)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H473" s="26" t="n">
@@ -30436,7 +30445,7 @@
         <v>0</v>
       </c>
       <c r="G474" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A474=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B474)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A474&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A474=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B474)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H474" s="26" t="n">
@@ -30482,7 +30491,7 @@
         <v>0</v>
       </c>
       <c r="G475" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A475=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B475)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A475&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A475=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B475)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H475" s="26" t="n">
@@ -30528,7 +30537,7 @@
         <v>0</v>
       </c>
       <c r="G476" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A476=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B476)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A476&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A476=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B476)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>1200</v>
       </c>
       <c r="H476" s="26" t="n">
@@ -30574,7 +30583,7 @@
         <v>0</v>
       </c>
       <c r="G477" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A477=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B477)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A477&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A477=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B477)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H477" s="26" t="n">
@@ -30620,7 +30629,7 @@
         <v>0</v>
       </c>
       <c r="G478" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A478=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B478)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A478&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A478=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B478)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H478" s="26" t="n">
@@ -30666,7 +30675,7 @@
         <v>0</v>
       </c>
       <c r="G479" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A479=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B479)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A479&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A479=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B479)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H479" s="26" t="n">
@@ -30712,7 +30721,7 @@
         <v>0</v>
       </c>
       <c r="G480" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A480=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B480)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A480&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A480=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B480)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H480" s="26" t="n">
@@ -30758,7 +30767,7 @@
         <v>0</v>
       </c>
       <c r="G481" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A481=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B481)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A481&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A481=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B481)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H481" s="26" t="n">
@@ -30804,7 +30813,7 @@
         <v>0</v>
       </c>
       <c r="G482" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A482=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B482)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A482&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A482=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B482)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H482" s="26" t="n">
@@ -30850,7 +30859,7 @@
         <v>0</v>
       </c>
       <c r="G483" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A483=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B483)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A483&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A483=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B483)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H483" s="26" t="n">
@@ -30896,7 +30905,7 @@
         <v>0</v>
       </c>
       <c r="G484" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A484=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B484)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A484&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A484=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B484)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H484" s="26" t="n">
@@ -30942,7 +30951,7 @@
         <v>0</v>
       </c>
       <c r="G485" s="26" t="n">
-        <f aca="false">ROUND(Calculator!$E$6+IF(A485=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B485)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
+        <f aca="false">ROUND(IF(A485&gt;=Calculator!$E$11,Calculator!$E$6,0)+IF(A485=Calculator!$E$8,Calculator!$E$7,0)+IF(MONTH(B485)=Calculator!$E$10,Calculator!$E$9,0),2)</f>
         <v>200</v>
       </c>
       <c r="H485" s="26" t="n">
@@ -30998,7 +31007,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -31011,7 +31020,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -31024,7 +31033,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -31037,36 +31046,36 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">Calculator!$B$9</f>
@@ -49336,7 +49345,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -49345,7 +49354,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -49354,24 +49363,24 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="5"/>
       <c r="D5" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">Calculator!$B$6</f>
         <v>420000</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>24</v>
@@ -49379,14 +49388,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">Calculator!$B$7</f>
         <v>0.065</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>0.0575</v>
@@ -49394,14 +49403,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">Calculator!$B$8</f>
         <v>30</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>30</v>
@@ -49409,14 +49418,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">Calculator!$H$6</f>
         <v>2654.69</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>4000</v>
@@ -49424,7 +49433,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -49433,7 +49442,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">INDEX(Baseline!H6:H485,E6)</f>
@@ -49442,7 +49451,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="11" t="n">
         <f aca="false">Baseline!I485-INDEX(Baseline!I6:I485,E6)</f>
@@ -49451,7 +49460,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">ROUND(PMT(E7/12,E8*12,-B12),2)</f>
@@ -49460,7 +49469,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">B14-B9</f>
@@ -49469,7 +49478,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">ROUND(B14*E8*12-B12,2)</f>
@@ -49478,7 +49487,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">B16+E9</f>
@@ -49487,7 +49496,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="26" t="n">
         <f aca="false">B9-B14</f>
@@ -49496,7 +49505,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="6" t="n">
         <f aca="false">IF(B18&lt;=0,"No payment savings",ROUNDUP(E9/B18,0))</f>
@@ -49505,7 +49514,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B20" s="8" t="str">
         <f aca="false">IF(B17&lt;B13,"Refinancing costs less than staying on the current loan.","Keeping the current loan costs less than refinancing.")</f>
@@ -49514,7 +49523,7 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="28"/>
       <c r="C22" s="28"/>
@@ -49557,7 +49566,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -49566,7 +49575,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -49575,7 +49584,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="5"/>
     </row>
@@ -49608,7 +49617,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">Calculator!$H$6</f>
@@ -49617,13 +49626,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">ROUND(B9*13/12,2)</f>
@@ -49632,7 +49641,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B13" s="29" t="n">
         <f aca="false">NPER(B7/12,-B12,B6)</f>
@@ -49641,7 +49650,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">B13/12</f>
@@ -49650,7 +49659,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">B8*12</f>
@@ -49668,7 +49677,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B17" s="11" t="n">
         <f aca="false">B12*B13-B6</f>
@@ -49677,7 +49686,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">Baseline!I485</f>
@@ -49695,13 +49704,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="32"/>
     </row>
     <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" s="28"/>
     </row>
@@ -49749,7 +49758,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -49767,7 +49776,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -49785,28 +49794,28 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B31" s="11" t="n">
         <f aca="false">SUMIFS(Schedule!$E$6:$E$485,Schedule!$C$6:$C$485,A31)</f>
